--- a/TOPIC_MAPPING.xlsx
+++ b/TOPIC_MAPPING.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Petya_\MEGAPROJECTS\VAP_RELEASE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4236A14-CCD7-4175-9562-AC7F7FDBB3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5408A33A-992F-4B71-940D-C538080AFEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="262">
   <si>
     <t>saludo</t>
   </si>
@@ -785,6 +785,27 @@
   </si>
   <si>
     <t>Obligatorio textual</t>
+  </si>
+  <si>
+    <t>Aviso de Privacidad</t>
+  </si>
+  <si>
+    <t>TRATAMIENTO DATOS</t>
+  </si>
+  <si>
+    <t>palabras prohibidas para activaci?n</t>
+  </si>
+  <si>
+    <t>palabras prohibidas para activación</t>
+  </si>
+  <si>
+    <t>pregunta de activaci?n de refuerzo</t>
+  </si>
+  <si>
+    <t>pregunta de activación de refuerzo</t>
+  </si>
+  <si>
+    <t>Pregunta de activación</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:FA341"/>
+  <dimension ref="A1:FA349"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.88671875" bestFit="1" customWidth="1"/>
@@ -4036,6 +4057,70 @@
         <v>157</v>
       </c>
     </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A342" t="s">
+        <v>255</v>
+      </c>
+      <c r="B342" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A343" t="s">
+        <v>258</v>
+      </c>
+      <c r="B343" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A344" t="s">
+        <v>248</v>
+      </c>
+      <c r="B344" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A345" t="s">
+        <v>257</v>
+      </c>
+      <c r="B345" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A346" t="s">
+        <v>260</v>
+      </c>
+      <c r="B346" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A347" t="s">
+        <v>249</v>
+      </c>
+      <c r="B347" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A348" t="s">
+        <v>259</v>
+      </c>
+      <c r="B348" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A349" t="s">
+        <v>261</v>
+      </c>
+      <c r="B349" t="s">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
